--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1593-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1593-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65CF7655-30E1-42F2-90B0-F62AE7097E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{496E93F3-A164-4400-88F8-34593AEE63EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5CCF62DD-7904-470F-B6BA-D5F87C283FEC}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{081BE187-6F87-4ED6-8212-C0322B8AA8A8}"/>
   </bookViews>
   <sheets>
     <sheet name="1593-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,28 +1571,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882DEE58-04C5-4ADC-8ECA-F0B0EB9E5CDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E91A414D-9AC0-4E48-90A7-B2DE7AE835CD}">
   <dimension ref="A1:X36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1626,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1782,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2024</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2023</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2022</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2021</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2020</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2019</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2018</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2017</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2016</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2015</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="41">
         <v>2014</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="43">
         <v>2013</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="45"/>
       <c r="B31" s="46"/>
       <c r="C31" s="20" t="s">
@@ -3708,7 +3708,7 @@
       <c r="W31" s="52"/>
       <c r="X31" s="48"/>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>2012</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="55"/>
       <c r="B33" s="56"/>
       <c r="C33" s="22" t="s">
@@ -3808,7 +3808,7 @@
       <c r="W33" s="62"/>
       <c r="X33" s="58"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2011</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2010</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39" t="s">
         <v>54</v>
       </c>
